--- a/ci-cd-merge-resolver/repoCollector/datasets/nacos.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/nacos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,42 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>67313bfe50551b5e9a6b737cdccc4d5cf865a952</t>
+  </si>
+  <si>
+    <t>daf3f43aa5aa4bba8f3ccb5304883146339b1c18</t>
+  </si>
+  <si>
+    <t>c2f15798d76e9260bfcf7ca670e146d8aa4be990</t>
+  </si>
+  <si>
+    <t>2537139feac51051938d76fa9eeebecd038aed20</t>
+  </si>
+  <si>
+    <t>8af465ad0d02d99a2a135eb913c6bc73060ec66c</t>
+  </si>
+  <si>
+    <t>e2d44f2fd2b12124d844d152b7025e3f758d00e6</t>
+  </si>
+  <si>
+    <t>fc8549dc8f9551462d6bf00b50233374159aaf58</t>
+  </si>
+  <si>
+    <t>ae148b86be716d04fc55793b18ed1a7f02715924</t>
+  </si>
+  <si>
+    <t>51b6a443d3bcf0ea42193930fff98f1bc5a86a26</t>
+  </si>
+  <si>
+    <t>0555619b05e1626907e4fd1afbdd856d2c1bac30</t>
+  </si>
+  <si>
+    <t>c7016893143c498b01c2fb725ec6ea843048dea0</t>
+  </si>
+  <si>
+    <t>dbe3730d6941908bae4a70105ff7088c10316185</t>
+  </si>
+  <si>
     <t>bcc942e59c64e16dd25e98af565042517a2d9905</t>
   </si>
   <si>
@@ -53,15 +89,6 @@
     <t>c0ee8ec0f791704ef4801ece46c8e7f54707d8c8</t>
   </si>
   <si>
-    <t>fc8549dc8f9551462d6bf00b50233374159aaf58</t>
-  </si>
-  <si>
-    <t>ae148b86be716d04fc55793b18ed1a7f02715924</t>
-  </si>
-  <si>
-    <t>51b6a443d3bcf0ea42193930fff98f1bc5a86a26</t>
-  </si>
-  <si>
     <t>5f7801b341b740671b127263d91684c8a6aa4807</t>
   </si>
   <si>
@@ -71,6 +98,33 @@
     <t>04f9b86e45b27ed2ebfce396bbcf855ba560b681</t>
   </si>
   <si>
+    <t>dccecd3b7620e5d6e611d2c336cb1d518d726b48</t>
+  </si>
+  <si>
+    <t>2b3fca3fbd76a82b7c4935d4655973786c3d739f</t>
+  </si>
+  <si>
+    <t>c5e5a8223167677a0df8d6e0cf9e16303faf58d6</t>
+  </si>
+  <si>
+    <t>b7fd0169240081b694b1d3a69a7470f94e0126c6</t>
+  </si>
+  <si>
+    <t>d75b1a2a9a041b61621180965d28d59c770ed82c</t>
+  </si>
+  <si>
+    <t>829e115606f62d71f0cd0dd04c533eb996b4dc61</t>
+  </si>
+  <si>
+    <t>a329625125e38322df88a029d6016d5f7495139a</t>
+  </si>
+  <si>
+    <t>678b90a91149b5757e4ee684c4be37f35eb2bc51</t>
+  </si>
+  <si>
+    <t>ed532b2d3c5c475125dfbf9c5a30aa2408829673</t>
+  </si>
+  <si>
     <t>6f3940735aeb2d96f74ecde7a2e6fe4c698ec718</t>
   </si>
   <si>
@@ -80,40 +134,31 @@
     <t>cb3685d084ea0b647a0d9a282cbbab40ab250809</t>
   </si>
   <si>
-    <t>0555619b05e1626907e4fd1afbdd856d2c1bac30</t>
-  </si>
-  <si>
-    <t>c7016893143c498b01c2fb725ec6ea843048dea0</t>
-  </si>
-  <si>
-    <t>dbe3730d6941908bae4a70105ff7088c10316185</t>
-  </si>
-  <si>
-    <t>2537139feac51051938d76fa9eeebecd038aed20</t>
-  </si>
-  <si>
-    <t>8af465ad0d02d99a2a135eb913c6bc73060ec66c</t>
-  </si>
-  <si>
-    <t>e2d44f2fd2b12124d844d152b7025e3f758d00e6</t>
-  </si>
-  <si>
-    <t>a329625125e38322df88a029d6016d5f7495139a</t>
-  </si>
-  <si>
-    <t>678b90a91149b5757e4ee684c4be37f35eb2bc51</t>
-  </si>
-  <si>
-    <t>ed532b2d3c5c475125dfbf9c5a30aa2408829673</t>
-  </si>
-  <si>
-    <t>67313bfe50551b5e9a6b737cdccc4d5cf865a952</t>
-  </si>
-  <si>
-    <t>daf3f43aa5aa4bba8f3ccb5304883146339b1c18</t>
-  </si>
-  <si>
-    <t>c2f15798d76e9260bfcf7ca670e146d8aa4be990</t>
+    <t>42b2a399e22c3f2c6eceacde7bff627b9320d4ec</t>
+  </si>
+  <si>
+    <t>0ff32de76f0301e5d85f635345c3ada7cc767183</t>
+  </si>
+  <si>
+    <t>595bdc9037b89bea68d27b3815c8fdc8f7ae39c0</t>
+  </si>
+  <si>
+    <t>aa6816b69f8d49a0391f2e24a0a8dd7cf56aae4a</t>
+  </si>
+  <si>
+    <t>94d812a269012ebd7f4e90ed8fc0f0bbd7c8d3b4</t>
+  </si>
+  <si>
+    <t>b1ac88be78b8b7eb23b54192c7e0ca07d54eeb1e</t>
+  </si>
+  <si>
+    <t>8410fbccf3b2a680cca2e96ad6b681f570fa5729</t>
+  </si>
+  <si>
+    <t>03345fd923c79ba2ca749076ce9a8dc38a496594</t>
+  </si>
+  <si>
+    <t>ee79d1b0606a1e57641c188e335af8729bee84de</t>
   </si>
   <si>
     <t>22169055ed7de07e6fa3a007125c4766aad9f6bd</t>
@@ -125,51 +170,6 @@
     <t>083464182579581b74f4ed39a5df54c598422053</t>
   </si>
   <si>
-    <t>8410fbccf3b2a680cca2e96ad6b681f570fa5729</t>
-  </si>
-  <si>
-    <t>03345fd923c79ba2ca749076ce9a8dc38a496594</t>
-  </si>
-  <si>
-    <t>ee79d1b0606a1e57641c188e335af8729bee84de</t>
-  </si>
-  <si>
-    <t>aa6816b69f8d49a0391f2e24a0a8dd7cf56aae4a</t>
-  </si>
-  <si>
-    <t>94d812a269012ebd7f4e90ed8fc0f0bbd7c8d3b4</t>
-  </si>
-  <si>
-    <t>b1ac88be78b8b7eb23b54192c7e0ca07d54eeb1e</t>
-  </si>
-  <si>
-    <t>b7fd0169240081b694b1d3a69a7470f94e0126c6</t>
-  </si>
-  <si>
-    <t>d75b1a2a9a041b61621180965d28d59c770ed82c</t>
-  </si>
-  <si>
-    <t>829e115606f62d71f0cd0dd04c533eb996b4dc61</t>
-  </si>
-  <si>
-    <t>42b2a399e22c3f2c6eceacde7bff627b9320d4ec</t>
-  </si>
-  <si>
-    <t>0ff32de76f0301e5d85f635345c3ada7cc767183</t>
-  </si>
-  <si>
-    <t>595bdc9037b89bea68d27b3815c8fdc8f7ae39c0</t>
-  </si>
-  <si>
-    <t>dccecd3b7620e5d6e611d2c336cb1d518d726b48</t>
-  </si>
-  <si>
-    <t>2b3fca3fbd76a82b7c4935d4655973786c3d739f</t>
-  </si>
-  <si>
-    <t>c5e5a8223167677a0df8d6e0cf9e16303faf58d6</t>
-  </si>
-  <si>
     <t>5b0b9665c37d1203edf4071aab3954ac0b56f1c7</t>
   </si>
   <si>
@@ -177,15 +177,6 @@
   </si>
   <si>
     <t>bb7e34e841d882ef9176a848bdd07a522be75d9b</t>
-  </si>
-  <si>
-    <t>94abf91680a9887ac45c2112319158aacf02ab23</t>
-  </si>
-  <si>
-    <t>09dc67a5e21f6238e1c950bf2dcdd1996913598d</t>
-  </si>
-  <si>
-    <t>12e305fb2eb25c99d33681a1347216a2407ba6c7</t>
   </si>
 </sst>
 </file>
@@ -230,7 +221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -276,13 +267,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>259.0</v>
+        <v>328.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>2.0</v>
+        <v>41.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>2.0</v>
+        <v>39.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -291,10 +282,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>6.198000431060791</v>
+        <v>14.586999893188477</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -308,13 +299,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>261.0</v>
+        <v>297.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -323,10 +314,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>2.9299991130828857</v>
+        <v>18.893001556396484</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -340,13 +331,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>280.0</v>
+        <v>279.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -355,10 +346,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>5.640997886657715</v>
+        <v>22.89400291442871</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -372,13 +363,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>280.0</v>
+        <v>277.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -387,10 +378,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>5.8759989738464355</v>
+        <v>16.617998123168945</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -404,13 +395,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>260.0</v>
+        <v>605.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -419,10 +410,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>17.08700180053711</v>
+        <v>81.09500122070312</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -436,13 +427,13 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>280.0</v>
+        <v>1055.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -451,10 +442,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>14.917999267578125</v>
+        <v>96.24201965332031</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -468,10 +459,10 @@
         <v>30</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>280.0</v>
+        <v>1056.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" t="n" s="0">
         <v>1.0</v>
@@ -483,10 +474,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>16.356998443603516</v>
+        <v>93.81900024414062</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -500,13 +491,13 @@
         <v>33</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>307.0</v>
+        <v>1056.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>41.0</v>
+        <v>8.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>39.0</v>
+        <v>3.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -515,10 +506,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>36.07699966430664</v>
+        <v>93.89900207519531</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +523,7 @@
         <v>36</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>229.0</v>
+        <v>1055.0</v>
       </c>
       <c r="E10" t="n" s="0">
         <v>1.0</v>
@@ -547,10 +538,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>42.369998931884766</v>
+        <v>96.219970703125</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +555,13 @@
         <v>39</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>241.0</v>
+        <v>1056.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
@@ -579,10 +570,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>62.89899826049805</v>
+        <v>94.76400756835938</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -596,13 +587,13 @@
         <v>42</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>237.0</v>
+        <v>1056.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" t="b" s="0">
         <v>0</v>
@@ -611,10 +602,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>59.224998474121094</v>
+        <v>97.85196685791016</v>
       </c>
       <c r="J12" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -628,10 +619,10 @@
         <v>45</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>280.0</v>
+        <v>308.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="F13" t="n" s="0">
         <v>3.0</v>
@@ -643,10 +634,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>6.072998046875</v>
+        <v>70.80699157714844</v>
       </c>
       <c r="J13" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -660,10 +651,10 @@
         <v>48</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>280.0</v>
+        <v>312.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F14" t="n" s="0">
         <v>1.0</v>
@@ -675,10 +666,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>4.506000518798828</v>
+        <v>75.04800415039062</v>
       </c>
       <c r="J14" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -692,10 +683,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>280.0</v>
+        <v>308.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F15" t="n" s="0">
         <v>1.0</v>
@@ -707,10 +698,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>12.135001182556152</v>
+        <v>72.71600341796875</v>
       </c>
       <c r="J15" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -724,7 +715,7 @@
         <v>54</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1080.0</v>
+        <v>2487.0</v>
       </c>
       <c r="E16" t="n" s="0">
         <v>8.0</v>
@@ -739,42 +730,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>102.1830062866211</v>
+        <v>302.96514892578125</v>
       </c>
       <c r="J16" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="D17" t="n" s="0">
-        <v>1119.0</v>
-      </c>
-      <c r="E17" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F17" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G17" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H17" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n" s="0">
-        <v>105.48896026611328</v>
-      </c>
-      <c r="J17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
